--- a/AAII_Financials/Quarterly/F_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/F_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>F</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>48296000</v>
+      </c>
+      <c r="E8" s="3">
         <v>43253000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>45890000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>50534000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>50184000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>40659000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>48211000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>46196000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>47808000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>42777000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>45962000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>43801000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>44954000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>41474000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>43999000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>39392000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>40190000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34476000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>37678000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>35683000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>26752000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>36228000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>35952000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>37501000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>19371000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>34320000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>39715000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>36990000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>38853000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>40342000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>41793000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>37666000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>38920000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>41959000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>41326000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>36451000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>39853000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>39146000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>38654000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>35943000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>42016000</v>
+      </c>
+      <c r="E9" s="3">
         <v>35311000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>42422000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>43411000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>44245000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>35188000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>41301000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>40168000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>40489000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>36476000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>40862000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>37548000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>37471000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>34669000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>39896000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>36009000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>34563000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>30393000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>33691000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>31394000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>23897000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>30921000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>34862000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>32881000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>20150000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>33443000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>37175000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>33851000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>36038000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>36297000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>38165000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>33920000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>35556000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>38091000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>37371000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>32534000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>35545000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>34918000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>34862000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>32868000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3536000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5291000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>579000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4311000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3230000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2760000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3980000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3346000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4561000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3609000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2539000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3809000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5218000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4627000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4103000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3383000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>5627000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4083000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3987000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4289000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2855000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>5307000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1090000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>4620000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-779000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>877000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2540000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3139000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2815000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4045000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3628000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3746000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3364000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3868000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3955000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>3917000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>4308000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>4228000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>3792000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>3075000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,19 +1219,20 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>9400000</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1227,11 +1240,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>8000000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1239,11 +1252,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>8200000</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,67 +1467,70 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>262000</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>8916000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-20000</v>
       </c>
-      <c r="G14" s="3">
-        <v>-12000</v>
-      </c>
       <c r="H14" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I14" s="3">
         <v>-39000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>29000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-49000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-38000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>22000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2425000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>22000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>99000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>47000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>167000</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>1702000</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1519,29 +1538,29 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>2000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>3000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>16000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>6000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>800000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>53000</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
@@ -1552,8 +1571,8 @@
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK14" s="3">
         <v>0</v>
@@ -1573,53 +1592,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1432000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1425000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1655000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1522000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1434000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1384000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1450000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1394000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1518000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1505000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1698000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1654000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1546000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1625000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>47387000</v>
+      </c>
+      <c r="E17" s="3">
         <v>40769000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48960000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>48944000</v>
       </c>
-      <c r="G17" s="3">
-        <v>49646000</v>
-      </c>
       <c r="H17" s="3">
+        <v>49635000</v>
+      </c>
+      <c r="I17" s="3">
         <v>40319000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>46331000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>45653000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>45820000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>41568000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>46900000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>42390000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>42319000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>39518000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>42438000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>39023000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>37322000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>33133000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>38641000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>34341000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>26774000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>33764000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>38394000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>35150000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22131000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>35878000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>40173000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>37252000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>38816000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>39140000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>41161000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>36802000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>38334000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>40838000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>40459000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>35453000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>38301000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>37682000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>37703000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>35525000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>909000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2484000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3070000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1590000</v>
       </c>
-      <c r="G18" s="3">
-        <v>538000</v>
-      </c>
       <c r="H18" s="3">
+        <v>549000</v>
+      </c>
+      <c r="I18" s="3">
         <v>340000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1880000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>543000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1988000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1209000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-938000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1411000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2635000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1956000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1561000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>369000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2868000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1343000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-963000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1342000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-22000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2464000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2442000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2351000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2760000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1558000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-458000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-262000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>37000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1202000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>632000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>864000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>586000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1121000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>867000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>998000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1552000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1464000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>951000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>418000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,213 +2056,217 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2608000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-778000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2812000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-157000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>81000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-196000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-359000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-183000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-324000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-307000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1433000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>86000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>314000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-214000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-77000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1173000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1765000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4883000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>12619000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>982000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1210000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1951000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-894000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>903000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4294000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>639000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1723000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>519000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>412000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>653000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-354000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>573000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1064000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1087000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>1313000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>1070000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>1005000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>1080000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-1824000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>1207000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-267000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4687000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4227000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3269000</v>
       </c>
-      <c r="G21" s="3">
-        <v>1891000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1902000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1920000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3689000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2120000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3830000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3021000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2193000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2979000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3867000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3795000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3457000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1091000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3020000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1683000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>13496000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4163000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2724000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6518000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1255000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5122000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3892000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1525000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>198000</v>
-      </c>
-      <c r="AD21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>8</v>
@@ -2238,404 +2274,416 @@
       <c r="AF21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH21" s="3">
         <v>4158000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1437000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1750000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3508000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>6302000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>2168000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2557000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>3744000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>3550000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1725000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>365000</v>
+      </c>
+      <c r="E22" s="3">
         <v>350000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>404000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>328000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>297000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>305000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>292000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>273000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>279000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>292000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>370000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>330000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>306000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>312000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>318000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>321000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>312000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>308000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>438000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>439000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>453000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>473000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>474000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>498000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>450000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>227000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>255000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>276000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>244000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>245000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>295000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>343000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>301000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>289000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>308000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>298000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>291000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>293000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>244000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>238000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2033000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2912000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14810000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1818000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>541000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>621000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2314000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>869000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2438000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1612000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1867000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1387000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2288000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2159000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1166000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1125000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>791000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3848000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>11218000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1885000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>735000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3942000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3810000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2756000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1084000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1146000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2436000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>205000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1610000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-17000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1094000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1349000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1919000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1872000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1770000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2266000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2251000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-1117000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1387000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-711000</v>
+      </c>
+      <c r="E24" s="3">
         <v>361000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3756000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-630000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>570000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>148000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>483000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-27000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>605000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>278000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1344000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>214000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>272000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>496000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-93000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-195000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>153000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-729000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1055000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>63000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>182000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>680000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1019000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>366000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-34000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>847000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-859000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-442000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>55000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>427000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>218000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>101000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>280000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>174000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-132000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>191000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>211000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>652000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-336000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>426000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1322000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2551000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11054000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2448000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-29000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>473000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1831000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>896000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1833000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1334000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-523000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1173000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2016000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1663000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1259000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-930000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>638000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3119000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>12273000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1822000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>553000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3262000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2791000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2390000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1118000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1993000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1577000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>423000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>150000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1183000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-235000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>993000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1069000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1745000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2004000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1579000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>2055000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1599000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-781000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>961000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1327000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2548000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11064000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2447000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-36000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>471000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1824000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>892000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1831000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1332000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-526000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1199000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1917000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1757000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1289000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-827000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>667000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3110000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>12282000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1832000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>561000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3262000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2788000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2385000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1117000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1993000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1577000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>425000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>148000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1146000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-239000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>991000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1066000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1736000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2000000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1572000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>2047000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1592000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-783000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>957000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3184,8 +3244,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -3202,11 +3262,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-95000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -3214,11 +3274,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>123000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3226,11 +3286,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>520000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,252 +3554,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2608000</v>
+      </c>
+      <c r="E32" s="3">
         <v>778000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2812000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>157000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-81000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>196000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>359000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>183000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>324000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>307000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1433000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-86000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-314000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>214000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>77000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1173000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1765000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4883000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-12619000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-982000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1210000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1951000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>894000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-903000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4294000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-639000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1723000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-519000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-412000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-653000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>354000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-573000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1064000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1087000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-1313000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-1070000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-1005000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-1080000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>1824000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-1207000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1327000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2548000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11064000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2447000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-36000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>471000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1824000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>892000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1831000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1332000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-526000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1199000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1917000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1757000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1289000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-827000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>667000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3110000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>12282000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1832000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>561000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3262000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2788000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2385000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1117000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1993000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>425000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>148000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1146000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-116000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>991000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1066000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1736000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2520000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1572000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>2047000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1592000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-783000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>957000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1327000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2548000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11064000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2447000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-36000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>471000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1824000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>892000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1831000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1332000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-526000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1199000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1917000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1757000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1289000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-827000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>667000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3110000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>12282000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1832000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>561000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3262000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2788000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2385000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1117000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1993000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>425000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>148000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1146000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-116000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>991000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1066000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1736000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2520000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1572000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>2047000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1592000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-783000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>957000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,984 +4276,1009 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10177000</v>
+      </c>
+      <c r="E41" s="3">
         <v>9725000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14086000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>18024000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14551000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13413000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13663000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14978000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12505000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10873000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>14204000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15776000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14945000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12829000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>25134000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>21548000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>19516000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>21013000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>20540000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>27429000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>22955000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>21826000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>25243000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>24263000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>30989000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>25971000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>17504000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>20523000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>22117000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>20848000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>16718000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>18562000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>16828000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>17940000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>18492000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>17589000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>16223000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>17823000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>15905000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>13340000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>11943000</v>
+      </c>
+      <c r="E42" s="3">
         <v>12054000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>14347000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>14647000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>13730000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>13581000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>14707000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>12729000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>13931000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>14028000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>14520000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>13224000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>14809000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>15794000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>18936000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>18625000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>17184000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>20215000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>29053000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>18997000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>18081000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>24281000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>24718000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>20568000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>26141000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>20399000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>17147000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>16808000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>15931000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>16882000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>17233000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>17780000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>19648000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>22131000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>20435000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>20492000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>22886000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>22166000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>22922000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>20825000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>17880000</v>
+      </c>
+      <c r="E43" s="3">
         <v>8375000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15398000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8267000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8373000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6572000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>14723000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5812000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6035000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5856000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>15601000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5966000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5070000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4342000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>54636000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>48798000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>45872000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>45928000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>44038000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>43576000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>43222000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>51276000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>52575000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>52145000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>52042000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>61753000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>62888000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>61804000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>64697000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>67460000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>65548000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>62062000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>62380000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>67066000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>62809000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>59818000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>60047000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>59290000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>57368000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>55579000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>16946000</v>
+      </c>
+      <c r="E44" s="3">
         <v>16537000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>15285000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>16509000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>17270000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>17895000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14951000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>18025000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>17183000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>18632000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>15651000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>18326000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>17703000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>16212000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>14080000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>15213000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>13976000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>14647000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>12065000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>13508000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>13593000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>12742000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>10808000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>10583000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>10220000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>11312000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>10786000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>12451000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>12437000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>12333000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>11220000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>12810000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>12565000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>12371000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>10277000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>11263000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>11092000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>10535000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>8898000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>10219000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4558000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4591000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3888000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3330000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3331000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3621000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4267000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3147000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3272000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3057000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3339000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2788000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2775000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3119000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3690000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3904000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3921000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4339000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3300000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3458000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3424000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3807000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3400000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4206000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4719000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4841000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5722000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4168000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3169000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3672000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3930000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3629000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3604000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3756000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3889000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>3570000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>3291000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>3414000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>3368000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>3552000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>117491000</v>
+      </c>
+      <c r="E46" s="3">
         <v>116329000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>123487000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>130720000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>126612000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>123054000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>124474000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>125099000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>120518000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>120595000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>121481000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>121361000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>121712000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>115123000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>116476000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>108088000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>100469000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>106142000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>108996000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>106968000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>101275000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>113932000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>116744000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>111765000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>124111000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>124276000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>114047000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>115754000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>118351000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>121195000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>114649000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>114843000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>115025000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>123264000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>116801000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>112732000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>113539000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>113228000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>108461000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>103515000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2615000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2595000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2628000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5227000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4896000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5030000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>6821000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7890000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7090000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>6212000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5548000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4277000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3464000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3327000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>53101000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>50639000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>55239000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>55506000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>56701000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>58367000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>59318000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>60064000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>60178000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>60400000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>58638000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>53416000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>56222000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>56153000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>56512000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>56937000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>58253000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>59901000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>59438000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>60334000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>59267000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>57667000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>54792000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>54336000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>53228000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>53409000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>41260000</v>
+      </c>
+      <c r="E48" s="3">
         <v>39709000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>38988000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>46466000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>45527000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>43607000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>45494000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>42092000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41590000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>41244000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>43706000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>40169000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>39272000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>38680000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>61484000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>59084000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>60695000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>62171000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>64837000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>63337000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>64285000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>64172000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>66321000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>64013000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>62992000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>63808000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>67114000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>66120000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>67678000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>66695000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>65297000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>65302000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>64945000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>64449000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>63562000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>63474000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>62391000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>60582000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>60901000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>61453000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5188,11 +5298,11 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>727000</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
@@ -5200,11 +5310,11 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>763000</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
@@ -5212,43 +5322,43 @@
         <v>0</v>
       </c>
       <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
         <v>603000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>575000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>595000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>617000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>619000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>695000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>741000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>566000</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>258000</v>
       </c>
       <c r="Z49" s="3">
         <v>258000</v>
       </c>
       <c r="AA49" s="3">
+        <v>258000</v>
+      </c>
+      <c r="AB49" s="3">
         <v>254000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>278000</v>
-      </c>
-      <c r="AC49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD49" s="3" t="s">
         <v>8</v>
@@ -5265,8 +5375,8 @@
       <c r="AH49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI49" s="3">
-        <v>0</v>
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ49" s="3">
         <v>0</v>
@@ -5289,8 +5399,11 @@
       <c r="AP49" s="3">
         <v>0</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11619000</v>
+      </c>
+      <c r="E52" s="3">
         <v>11791000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11536000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12503000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12383000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12284000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9430000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11218000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10791000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10737000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8391000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11285000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10889000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10289000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>24220000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>28533000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>28757000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>28550000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>25882000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>23310000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>22913000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>22085000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>23760000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>23507000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>23371000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>22372000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>21154000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>20130000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>19643000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>18454000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>18341000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>18920000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>18671000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>19183000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>18866000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>17400000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>16747000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>15948000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>15361000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>16586000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>285531000</v>
+      </c>
+      <c r="E54" s="3">
         <v>282434000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>289160000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>300990000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>292725000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>284539000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>285196000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>287047000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>276586000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>274341000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>273310000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>268073000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>265991000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>256800000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>255884000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>246919000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>245755000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>252986000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>257035000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>252677000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>248532000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>260819000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>267261000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>259943000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>269366000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>264150000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>258537000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>258157000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>262184000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>263281000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>256540000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>258966000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>258079000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>267230000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>258496000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>251273000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>247469000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>244094000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>237951000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>234963000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,740 +6116,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>26074000</v>
+      </c>
+      <c r="E57" s="3">
         <v>25052000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>24845000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>26953000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>26795000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>25305000</v>
       </c>
-      <c r="I57" s="3" t="s">
+      <c r="J57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>26501000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24550000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>26426000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>25992000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>26808000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>26711000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>24992000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>25605000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>27051000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>23378000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>23256000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>22349000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>22923000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>18593000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>23492000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>22204000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>21466000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>16360000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>18439000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>20673000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>22228000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>22980000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>23325000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>21520000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>23273000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>22743000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>25480000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>23282000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>23566000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>23568000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>23257000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>21296000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>21993000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>51888000</v>
+      </c>
+      <c r="E58" s="3">
         <v>51358000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>57869000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>58206000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>57456000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>55020000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>55507000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>54085000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>51070000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>50288000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>50150000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>49111000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>49754000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>48465000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>50164000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>44050000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>43819000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>48286000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>49692000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>47323000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>46012000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>49471000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>51343000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>50995000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>55344000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>52912000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>53946000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>54604000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>52851000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>54548000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>53493000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>50763000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>50884000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>52983000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>54977000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>51174000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>50773000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>49257000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>49669000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>47273000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>26471000</v>
+      </c>
+      <c r="E59" s="3">
         <v>26745000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>28551000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28035000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>27156000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24857000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>46999000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>23238000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>23895000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22604000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21347000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>20442000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20624000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18955000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21097000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>19066000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>19255000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18810000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>18686000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18787000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>18869000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>21286000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>23645000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>20698000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>21076000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>23143000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>23513000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>22255000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>22503000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>21364000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>20556000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>20714000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>21234000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>21415000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>28263000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>19612000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>19958000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>18790000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>19316000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>19922000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>107933000</v>
+      </c>
+      <c r="E60" s="3">
         <v>106679000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>114890000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>116648000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>114988000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>108732000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>106859000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>109036000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>103403000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>103206000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>101531000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>100268000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>101015000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>95905000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>96866000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>90167000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>86452000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>90352000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>90727000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>89033000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>83474000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>94249000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>97192000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>93159000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>92780000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>94494000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>98132000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>99087000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>98334000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>99237000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>95569000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>94750000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>94861000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>99878000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>94600000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>94352000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>94299000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>91304000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>90281000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>89188000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>21016000</v>
+      </c>
+      <c r="E61" s="3">
         <v>18145000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18204000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>19721000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18670000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18577000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>20680000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20628000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>20183000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>20940000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>20862000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>20740000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>20370000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>20391000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>88805000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>84279000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>85008000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>87315000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>88400000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>97249000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>100905000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>103201000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>110341000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>106280000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>119886000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>114414000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>101361000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>99507000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>103213000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>102612000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>100720000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>102668000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>101959000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>105351000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>102666000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>97938000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>95236000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>96720000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>93301000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>89951000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>27495000</v>
+      </c>
+      <c r="E62" s="3">
         <v>27112000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>27710000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>27587000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>26785000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>25498000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12784000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11865000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>25135000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24491000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10383000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24175000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>22458000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>22713000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>27046000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>30384000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>30058000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>30235000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>29286000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>29691000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>29369000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>29395000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>28917000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>27343000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>25845000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>25544000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>25814000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>24176000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>24501000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>24863000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>24185000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>24830000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>24691000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>25467000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>47766000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>25623000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>25575000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>25332000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>25086000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>24229000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>249776000</v>
+      </c>
+      <c r="E66" s="3">
         <v>244950000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>253180000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>253573000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>247644000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>239879000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>240338000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>242708000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>232991000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>231444000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>230512000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>223797000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>222385000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>214603000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>212642000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>204794000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>201586000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>208001000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>208516000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>216084000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>213868000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>226991000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>236571000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>226818000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>238542000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>234500000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>225352000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>222808000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>226087000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>226883000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>220608000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>222376000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>221638000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>230830000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>222918000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>218035000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>215225000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>213475000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>208781000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>203479000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>22508000</v>
+      </c>
+      <c r="E72" s="3">
         <v>24445000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>22508000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>34186000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>32352000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>32999000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>33740000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>32525000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>32240000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>31019000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>31029000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>32169000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>31577000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>30270000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>31754000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>31072000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>32511000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>32251000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>35769000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>23894000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>22062000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>21502000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>18243000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>21031000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18645000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>17527000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>20320000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>22590000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>22769000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>23226000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>22668000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>23384000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>22993000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>22529000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>21906000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>19405000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>18437000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>16992000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>15634000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>17013000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>35719000</v>
+      </c>
+      <c r="E76" s="3">
         <v>37453000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>35952000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>47392000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>45057000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>44635000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>44835000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>44315000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>43567000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>42870000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>42773000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>44263000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>43677000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>42366000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>43242000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>42125000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>44169000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>44985000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>48519000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>36593000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>34664000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>33828000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>30690000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>33125000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>30824000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>29650000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>33185000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>35349000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>36097000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>36398000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>35932000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>36590000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>36441000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>36400000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>35578000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>33238000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>32244000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>30619000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>29170000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>31484000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1327000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2548000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11064000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2447000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-36000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>471000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1824000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>892000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1831000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1332000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-526000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1199000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1917000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1757000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1289000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-827000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>667000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3110000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>12282000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1832000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>561000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3262000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2788000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2385000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1117000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1993000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>425000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>148000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1146000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-116000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>991000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1066000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1736000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2520000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1572000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>2047000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1592000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-783000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>957000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,91 +8961,92 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1434000</v>
+      </c>
+      <c r="E83" s="3">
         <v>1384000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1450000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1394000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1518000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1505000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1698000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1654000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1546000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1625000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1668000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1627000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1619000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1547000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1973000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1895000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1917000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1857000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1840000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1839000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1536000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2103000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2081000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1868000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2358000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2444000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2379000</v>
-      </c>
-      <c r="AD83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>8</v>
@@ -8865,8 +9063,8 @@
       <c r="AI83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ83" s="3">
-        <v>0</v>
+      <c r="AJ83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK83" s="3">
         <v>0</v>
@@ -8886,8 +9084,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4345000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1316000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3884000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7402000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6317000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3679000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3028000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5502000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5508000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1385000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2492000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4591000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5035000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2800000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1178000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3812000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2947000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1084000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3531000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>7008000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>756000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4492000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4539000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>11088000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>9115000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-473000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2900000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4732000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>6463000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3544000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1357000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>5179000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>4972000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>3514000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3147000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>4998000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>5615000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>4336000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>2740000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>5161000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2382000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2376000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2784000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2125000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2088000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1818000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2498000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1992000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2100000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2094000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2295000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2212000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1949000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1780000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2065000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1732000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1699000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1370000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1772000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1574000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1513000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1368000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1531000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1256000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1175000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1780000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2274000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1805000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1920000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1633000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2116000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1981000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1909000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1779000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2113000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1672000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-1558000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-3412000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>2832000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-3412000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3247000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-771000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7661000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7377000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3221000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>210000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6861000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5588000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6041000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5880000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7409000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4062000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4180000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1977000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4972000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3517000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>827000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>3315000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2263000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1170000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>6669000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-491000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5745000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>1345000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-11101000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3114000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5350000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4547000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2490000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1334000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3666000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3573000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2478000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-6544000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-6835000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-3663000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-5223000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-3639000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-7294000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-5949000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,77 +10426,78 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>599000</v>
+      </c>
+      <c r="E96" s="3">
         <v>607000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1200</v>
-      </c>
-      <c r="F96" s="3">
-        <v>597000</v>
       </c>
       <c r="G96" s="3">
         <v>597000</v>
       </c>
       <c r="H96" s="3">
+        <v>597000</v>
+      </c>
+      <c r="I96" s="3">
         <v>1196000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>597000</v>
       </c>
-      <c r="J96" s="3" t="s">
+      <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>599000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>1326000</v>
       </c>
-      <c r="M96" s="3" t="s">
+      <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>600000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>601000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>3193000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-599000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-603000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-402000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-405000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-400000</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -10272,19 +10505,19 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-596000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-595000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-598000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-599000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-597000</v>
       </c>
       <c r="AG96" s="3">
         <v>-597000</v>
@@ -10293,31 +10526,34 @@
         <v>-597000</v>
       </c>
       <c r="AI96" s="3">
+        <v>-597000</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-598000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-1113000</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-596000</v>
       </c>
       <c r="AL96" s="3">
         <v>-596000</v>
       </c>
       <c r="AM96" s="3">
+        <v>-596000</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-597000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-795000</v>
-      </c>
-      <c r="AO96" s="3">
-        <v>-596000</v>
       </c>
       <c r="AP96" s="3">
         <v>-596000</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-596000</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-198000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6172000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>353000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3850000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1288000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6120000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3790000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3311000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>842000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-458000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3383000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-338000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3413000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3874000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>7055000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1696000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4579000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1661000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-8078000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1222000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6405000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-7793000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2284000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-19360000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>6937000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>12454000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-689000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1632000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2681000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1873000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>526000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>144000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-3206000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>2414000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>4559000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-127000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2158000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>1120000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>7290000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-2877000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>365000</v>
+      </c>
+      <c r="E101" s="3">
         <v>118000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-493000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>275000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-69000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-171000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>10000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-180000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>70000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>358000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-404000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-344000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-24000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>358000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-404000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-344000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-24000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-77000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-154000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>92000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-93000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>385000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>218000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>70000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-448000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>199000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-178000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>29000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-65000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-404000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>115000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>47000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>175000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>166000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>101000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-229000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-57000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>893000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5747000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3334000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3834000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2173000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2113000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-536000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3500000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>240000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5124000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1524000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>11000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4264000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2981000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3619000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1587000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1149000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>546000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6887000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4462000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1112000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3885000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1463000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6709000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5021000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>8419000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2940000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1625000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1287000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4112000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1848000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1734000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1116000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-501000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>918000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1383000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-1600000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1918000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>2565000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-3723000</v>
       </c>
     </row>
